--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>81.74053762698152</v>
+        <v>13.2828373643845</v>
       </c>
       <c r="D2" t="n">
-        <v>55.86068816563951</v>
+        <v>9.077361826916421</v>
       </c>
       <c r="E2" t="n">
-        <v>14.51107186939872</v>
+        <v>2.358049178777292</v>
       </c>
       <c r="F2" t="n">
-        <v>12.75103285502244</v>
+        <v>2.072042838941146</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.57135279929093</v>
+        <v>8.705344829884776</v>
       </c>
       <c r="D3" t="n">
-        <v>52.03010319237541</v>
+        <v>8.454891768761005</v>
       </c>
       <c r="E3" t="n">
-        <v>14.51107186939872</v>
+        <v>2.358049178777292</v>
       </c>
       <c r="F3" t="n">
-        <v>12.75103285502244</v>
+        <v>2.072042838941146</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.69631504974593</v>
+        <v>6.450651195583713</v>
       </c>
       <c r="D4" t="n">
-        <v>22.07413155597786</v>
+        <v>3.587046377846403</v>
       </c>
       <c r="E4" t="n">
-        <v>14.51107186939872</v>
+        <v>2.358049178777292</v>
       </c>
       <c r="F4" t="n">
-        <v>12.75103285502244</v>
+        <v>2.072042838941146</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.44539380903576</v>
+        <v>6.084876493968312</v>
       </c>
       <c r="D5" t="n">
-        <v>36.06412043930771</v>
+        <v>5.860419571387503</v>
       </c>
       <c r="E5" t="n">
-        <v>14.51107186939872</v>
+        <v>2.358049178777292</v>
       </c>
       <c r="F5" t="n">
-        <v>12.75103285502244</v>
+        <v>2.072042838941146</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.86971916493636</v>
+        <v>9.403829364302158</v>
       </c>
       <c r="D6" t="n">
-        <v>56.76696976316737</v>
+        <v>9.224632586514698</v>
       </c>
       <c r="E6" t="n">
-        <v>14.51107186939872</v>
+        <v>2.358049178777292</v>
       </c>
       <c r="F6" t="n">
-        <v>12.75103285502244</v>
+        <v>2.072042838941146</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.71503681863119</v>
+        <v>8.728693483027568</v>
       </c>
       <c r="D7" t="n">
-        <v>53.40594315430818</v>
+        <v>8.67846576257508</v>
       </c>
       <c r="E7" t="n">
-        <v>14.51107186939872</v>
+        <v>2.358049178777292</v>
       </c>
       <c r="F7" t="n">
-        <v>12.75103285502244</v>
+        <v>2.072042838941146</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
